--- a/data/pOXA48/rep1/summary flowcyto with events.xlsx
+++ b/data/pOXA48/rep1/summary flowcyto with events.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vuhien/Desktop/1st rep Chibio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/storage/hien/Hien PhD project new/Result/Full lab evolution exp/pOXA48 plasmid/20251106 1st rep/Flow cytometry/Analyzed data 100x dilutions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1A9FD6-42F5-9045-A1D1-3C391CE0C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE61EE0-6024-3343-A830-6626DEF90F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="208">
   <si>
     <t>vial</t>
   </si>
@@ -162,9 +162,6 @@
     <t>5,05 %</t>
   </si>
   <si>
-    <t>150h</t>
-  </si>
-  <si>
     <t>60,5 %</t>
   </si>
   <si>
@@ -183,12 +180,6 @@
     <t>15,6 %</t>
   </si>
   <si>
-    <t>174h</t>
-  </si>
-  <si>
-    <t>198h</t>
-  </si>
-  <si>
     <t>57,0 %</t>
   </si>
   <si>
@@ -649,6 +640,15 @@
   </si>
   <si>
     <t>8,14 %</t>
+  </si>
+  <si>
+    <t>160h</t>
+  </si>
+  <si>
+    <t>184h</t>
+  </si>
+  <si>
+    <t>208h</t>
   </si>
 </sst>
 </file>
@@ -689,15 +689,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -928,12 +927,12 @@
         <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="4">
+        <v>55</v>
+      </c>
+      <c r="F2" s="1">
         <v>85619</v>
       </c>
     </row>
@@ -945,15 +944,15 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="4">
+        <v>52</v>
+      </c>
+      <c r="F3" s="1">
         <v>65263</v>
       </c>
     </row>
@@ -965,15 +964,15 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1">
         <v>84952</v>
       </c>
     </row>
@@ -988,12 +987,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="4">
+        <v>61</v>
+      </c>
+      <c r="F5" s="1">
         <v>74075</v>
       </c>
     </row>
@@ -1005,15 +1004,15 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="4">
+        <v>63</v>
+      </c>
+      <c r="F6" s="1">
         <v>104942</v>
       </c>
     </row>
@@ -1025,15 +1024,15 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="4">
+        <v>65</v>
+      </c>
+      <c r="F7" s="1">
         <v>101358</v>
       </c>
     </row>
@@ -1045,15 +1044,15 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="4">
+        <v>68</v>
+      </c>
+      <c r="F8" s="1">
         <v>87137</v>
       </c>
     </row>
@@ -1073,7 +1072,7 @@
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <v>83837</v>
       </c>
     </row>
@@ -1085,15 +1084,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="5">
+        <v>68</v>
+      </c>
+      <c r="F10" s="4">
         <v>84741</v>
       </c>
     </row>
@@ -1105,15 +1104,15 @@
         <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="5">
+        <v>73</v>
+      </c>
+      <c r="F11" s="4">
         <v>56680</v>
       </c>
     </row>
@@ -1125,15 +1124,15 @@
         <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="5">
+        <v>76</v>
+      </c>
+      <c r="F12" s="4">
         <v>96926</v>
       </c>
     </row>
@@ -1145,15 +1144,15 @@
         <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="5">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4">
         <v>59691</v>
       </c>
     </row>
@@ -1168,12 +1167,12 @@
         <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="5">
+        <v>80</v>
+      </c>
+      <c r="F14" s="4">
         <v>76571</v>
       </c>
     </row>
@@ -1185,15 +1184,15 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="5">
+        <v>83</v>
+      </c>
+      <c r="F15" s="4">
         <v>88708</v>
       </c>
     </row>
@@ -1205,15 +1204,15 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="5">
+        <v>84</v>
+      </c>
+      <c r="F16" s="4">
         <v>72361</v>
       </c>
     </row>
@@ -1225,15 +1224,15 @@
         <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="5">
+        <v>76</v>
+      </c>
+      <c r="F17" s="4">
         <v>59237</v>
       </c>
     </row>
@@ -1245,15 +1244,15 @@
         <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="5">
+        <v>88</v>
+      </c>
+      <c r="F18" s="4">
         <v>50121</v>
       </c>
     </row>
@@ -1265,15 +1264,15 @@
         <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="5">
+        <v>91</v>
+      </c>
+      <c r="F19" s="4">
         <v>24999</v>
       </c>
     </row>
@@ -1285,15 +1284,15 @@
         <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="5">
+        <v>93</v>
+      </c>
+      <c r="F20" s="4">
         <v>64823</v>
       </c>
     </row>
@@ -1305,15 +1304,15 @@
         <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="5">
+        <v>96</v>
+      </c>
+      <c r="F21" s="4">
         <v>63701</v>
       </c>
     </row>
@@ -1325,15 +1324,15 @@
         <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="5">
+        <v>97</v>
+      </c>
+      <c r="F22" s="4">
         <v>65723</v>
       </c>
     </row>
@@ -1345,7 +1344,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>28</v>
@@ -1353,7 +1352,7 @@
       <c r="E23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>96854</v>
       </c>
     </row>
@@ -1365,15 +1364,15 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="5">
+        <v>99</v>
+      </c>
+      <c r="F24" s="4">
         <v>44670</v>
       </c>
     </row>
@@ -1385,15 +1384,15 @@
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>38148</v>
       </c>
     </row>
@@ -1405,15 +1404,15 @@
         <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="5">
+        <v>102</v>
+      </c>
+      <c r="F26" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1428,12 +1427,12 @@
         <v>44</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="5">
+        <v>104</v>
+      </c>
+      <c r="F27" s="4">
         <v>21389</v>
       </c>
     </row>
@@ -1445,15 +1444,15 @@
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>183343</v>
       </c>
     </row>
@@ -1465,15 +1464,15 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="5">
+        <v>109</v>
+      </c>
+      <c r="F29" s="4">
         <v>50749</v>
       </c>
     </row>
@@ -1485,15 +1484,15 @@
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="5">
+        <v>112</v>
+      </c>
+      <c r="F30" s="4">
         <v>133837</v>
       </c>
     </row>
@@ -1505,15 +1504,15 @@
         <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="5">
+        <v>113</v>
+      </c>
+      <c r="F31" s="4">
         <v>90181</v>
       </c>
     </row>
@@ -1525,15 +1524,15 @@
         <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="5">
+        <v>115</v>
+      </c>
+      <c r="F32" s="4">
         <v>160242</v>
       </c>
     </row>
@@ -1545,15 +1544,15 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="5">
+        <v>117</v>
+      </c>
+      <c r="F33" s="4">
         <v>172820</v>
       </c>
     </row>
@@ -1564,7 +1563,18 @@
       <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="C34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -1574,15 +1584,15 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="4">
+        <v>59</v>
+      </c>
+      <c r="F35" s="1">
         <v>12136</v>
       </c>
     </row>
@@ -1594,15 +1604,15 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" s="4">
+        <v>120</v>
+      </c>
+      <c r="F36" s="1">
         <v>100085</v>
       </c>
     </row>
@@ -1614,15 +1624,15 @@
         <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F37" s="4">
+        <v>123</v>
+      </c>
+      <c r="F37" s="1">
         <v>28637</v>
       </c>
     </row>
@@ -1634,15 +1644,15 @@
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="4">
+        <v>125</v>
+      </c>
+      <c r="F38" s="1">
         <v>50682</v>
       </c>
     </row>
@@ -1654,15 +1664,15 @@
         <v>33</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F39" s="4">
+        <v>128</v>
+      </c>
+      <c r="F39" s="1">
         <v>37132</v>
       </c>
     </row>
@@ -1674,15 +1684,15 @@
         <v>33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F40" s="4">
+        <v>131</v>
+      </c>
+      <c r="F40" s="1">
         <v>94142</v>
       </c>
     </row>
@@ -1694,15 +1704,15 @@
         <v>33</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="4">
+        <v>115</v>
+      </c>
+      <c r="F41" s="1">
         <v>90594</v>
       </c>
     </row>
@@ -1713,7 +1723,18 @@
       <c r="B42" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="5"/>
+      <c r="C42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -1723,15 +1744,15 @@
         <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" s="5">
+        <v>84</v>
+      </c>
+      <c r="F43" s="4">
         <v>9142</v>
       </c>
     </row>
@@ -1743,15 +1764,15 @@
         <v>37</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F44" s="5">
+        <v>137</v>
+      </c>
+      <c r="F44" s="4">
         <v>96879</v>
       </c>
     </row>
@@ -1763,15 +1784,15 @@
         <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" s="5">
+        <v>73</v>
+      </c>
+      <c r="F45" s="4">
         <v>28382</v>
       </c>
     </row>
@@ -1783,15 +1804,15 @@
         <v>37</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F46" s="5">
+        <v>141</v>
+      </c>
+      <c r="F46" s="4">
         <v>43062</v>
       </c>
     </row>
@@ -1803,15 +1824,15 @@
         <v>37</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <v>50253</v>
       </c>
     </row>
@@ -1823,15 +1844,15 @@
         <v>37</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F48" s="5">
+        <v>145</v>
+      </c>
+      <c r="F48" s="4">
         <v>60927</v>
       </c>
     </row>
@@ -1843,15 +1864,15 @@
         <v>37</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="5">
+        <v>148</v>
+      </c>
+      <c r="F49" s="4">
         <v>87554</v>
       </c>
     </row>
@@ -1862,7 +1883,18 @@
       <c r="B50" t="s">
         <v>42</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="C50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
@@ -1872,15 +1904,15 @@
         <v>42</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="1">
         <v>4899</v>
       </c>
     </row>
@@ -1895,12 +1927,12 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F52" s="4">
+        <v>152</v>
+      </c>
+      <c r="F52" s="1">
         <v>80096</v>
       </c>
     </row>
@@ -1912,7 +1944,7 @@
         <v>42</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>17</v>
@@ -1920,7 +1952,7 @@
       <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="1">
         <v>25495</v>
       </c>
     </row>
@@ -1932,15 +1964,15 @@
         <v>42</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="1">
         <v>28298</v>
       </c>
     </row>
@@ -1952,15 +1984,15 @@
         <v>42</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F55" s="4">
+        <v>157</v>
+      </c>
+      <c r="F55" s="1">
         <v>92084</v>
       </c>
     </row>
@@ -1975,12 +2007,12 @@
         <v>39</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F56" s="4">
+        <v>159</v>
+      </c>
+      <c r="F56" s="1">
         <v>35535</v>
       </c>
     </row>
@@ -1992,15 +2024,15 @@
         <v>42</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F57" s="4">
+        <v>161</v>
+      </c>
+      <c r="F57" s="1">
         <v>54750</v>
       </c>
     </row>
@@ -2009,27 +2041,38 @@
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
-      </c>
-      <c r="F58" s="5"/>
+        <v>205</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="4">
         <v>3343</v>
       </c>
     </row>
@@ -2038,18 +2081,18 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F60" s="5">
+        <v>164</v>
+      </c>
+      <c r="F60" s="4">
         <v>48667</v>
       </c>
     </row>
@@ -2058,18 +2101,18 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F61" s="5">
+        <v>167</v>
+      </c>
+      <c r="F61" s="4">
         <v>22999</v>
       </c>
     </row>
@@ -2078,18 +2121,18 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F62" s="5">
+        <v>168</v>
+      </c>
+      <c r="F62" s="4">
         <v>39602</v>
       </c>
     </row>
@@ -2098,18 +2141,18 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F63" s="5">
+        <v>171</v>
+      </c>
+      <c r="F63" s="4">
         <v>66588</v>
       </c>
     </row>
@@ -2118,18 +2161,18 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F64" s="5">
+        <v>159</v>
+      </c>
+      <c r="F64" s="4">
         <v>25076</v>
       </c>
     </row>
@@ -2138,18 +2181,18 @@
         <v>19</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F65" s="5">
+        <v>172</v>
+      </c>
+      <c r="F65" s="4">
         <v>41119</v>
       </c>
     </row>
@@ -2158,27 +2201,38 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
-      </c>
-      <c r="F66" s="5"/>
+        <v>206</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F67" s="5">
+        <v>174</v>
+      </c>
+      <c r="F67" s="4">
         <v>2447</v>
       </c>
     </row>
@@ -2187,18 +2241,18 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F68" s="5">
+        <v>177</v>
+      </c>
+      <c r="F68" s="4">
         <v>35186</v>
       </c>
     </row>
@@ -2207,18 +2261,18 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F69" s="5">
+        <v>84</v>
+      </c>
+      <c r="F69" s="4">
         <v>22334</v>
       </c>
     </row>
@@ -2227,18 +2281,18 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F70" s="5">
+        <v>182</v>
+      </c>
+      <c r="F70" s="4">
         <v>35043</v>
       </c>
     </row>
@@ -2247,18 +2301,18 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F71" s="5">
+        <v>185</v>
+      </c>
+      <c r="F71" s="4">
         <v>41011</v>
       </c>
       <c r="J71" s="3"/>
@@ -2268,18 +2322,18 @@
         <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F72" s="5">
+        <v>188</v>
+      </c>
+      <c r="F72" s="4">
         <v>20998</v>
       </c>
       <c r="J72" s="3"/>
@@ -2289,18 +2343,18 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F73" s="5">
+        <v>189</v>
+      </c>
+      <c r="F73" s="4">
         <v>24318</v>
       </c>
     </row>
@@ -2309,27 +2363,38 @@
         <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
-      </c>
-      <c r="F74" s="5"/>
+        <v>207</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F75" s="4">
+        <v>191</v>
+      </c>
+      <c r="F75" s="1">
         <v>251</v>
       </c>
     </row>
@@ -2338,18 +2403,18 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F76" s="4">
+        <v>194</v>
+      </c>
+      <c r="F76" s="1">
         <v>8380</v>
       </c>
     </row>
@@ -2358,18 +2423,18 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F77" s="4">
+        <v>46</v>
+      </c>
+      <c r="F77" s="1">
         <v>11760</v>
       </c>
     </row>
@@ -2378,18 +2443,18 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F78" s="4">
+        <v>198</v>
+      </c>
+      <c r="F78" s="1">
         <v>10909</v>
       </c>
     </row>
@@ -2398,18 +2463,18 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F79" s="4">
+        <v>200</v>
+      </c>
+      <c r="F79" s="1">
         <v>10723</v>
       </c>
     </row>
@@ -2418,18 +2483,18 @@
         <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F80" s="4">
+        <v>202</v>
+      </c>
+      <c r="F80" s="1">
         <v>5726</v>
       </c>
     </row>
@@ -2438,18 +2503,18 @@
         <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F81" s="4">
+        <v>204</v>
+      </c>
+      <c r="F81" s="1">
         <v>3017</v>
       </c>
     </row>
